--- a/Producao/Producao-modelo.xlsx
+++ b/Producao/Producao-modelo.xlsx
@@ -2224,11 +2224,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="26565026"/>
-        <c:axId val="73853988"/>
+        <c:axId val="29397733"/>
+        <c:axId val="56989517"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="26565026"/>
+        <c:axId val="29397733"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2260,7 +2260,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73853988"/>
+        <c:crossAx val="56989517"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2268,7 +2268,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="73853988"/>
+        <c:axId val="56989517"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -2309,7 +2309,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26565026"/>
+        <c:crossAx val="29397733"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="0.25"/>

--- a/Producao/Producao-modelo.xlsx
+++ b/Producao/Producao-modelo.xlsx
@@ -163,7 +163,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="468">
   <si>
     <t xml:space="preserve">Controle de produção e de serviço — Como usar esta planilha</t>
   </si>
@@ -915,7 +915,7 @@
     <t xml:space="preserve">Termômetro da câmara, leitura no visor</t>
   </si>
   <si>
-    <t xml:space="preserve">Duas vezes por turno</t>
+    <t xml:space="preserve">Duas leituras por noite</t>
   </si>
   <si>
     <t xml:space="preserve">Pizzaiolo do turno · Planilha de temperatura (FR-02)</t>
@@ -939,7 +939,7 @@
     <t xml:space="preserve">Balança da bancada, média de cinco bolas</t>
   </si>
   <si>
-    <t xml:space="preserve">Cada lote de massa</t>
+    <t xml:space="preserve">Uma vez por noite, no lote de massa do dia</t>
   </si>
   <si>
     <t xml:space="preserve">Pizzaiolo do turno · Ficha do lote de massa</t>
@@ -960,7 +960,7 @@
     <t xml:space="preserve">Lista de abertura do turno, conferida no posto</t>
   </si>
   <si>
-    <t xml:space="preserve">Cada turno</t>
+    <t xml:space="preserve">Uma vez por noite, na abertura</t>
   </si>
   <si>
     <t xml:space="preserve">Pizzaiolo líder · Lista de abertura do turno</t>
@@ -978,7 +978,7 @@
     <t xml:space="preserve">Termômetro do forno, no pico do turno</t>
   </si>
   <si>
-    <t xml:space="preserve">Uma vez por hora</t>
+    <t xml:space="preserve">Uma vez por noite, no pico</t>
   </si>
   <si>
     <t xml:space="preserve">Pizzaiolo do turno · Registro de regulagem do forno</t>
@@ -996,16 +996,16 @@
     <t xml:space="preserve">pedidos</t>
   </si>
   <si>
-    <t xml:space="preserve">Conferência da pizza com a etiqueta; amostra de 20 no fechamento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Todo pedido</t>
+    <t xml:space="preserve">Conferência da pizza com a etiqueta, na saída, antes de o pedido sair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uma amostra de 20 pedidos por noite, somada no fechamento</t>
   </si>
   <si>
     <t xml:space="preserve">Quem embala · Etiqueta rubricada</t>
   </si>
   <si>
-    <t xml:space="preserve">Conferir de novo o pedido sem rubrica antes da saída e orientar quem embalou.</t>
+    <t xml:space="preserve">Segurar na saída o pedido sem rubrica, conferir com a etiqueta e orientar quem embalou.</t>
   </si>
   <si>
     <t xml:space="preserve">Expedir</t>
@@ -1020,7 +1020,7 @@
     <t xml:space="preserve">Horários de pronto e de saída, no sistema de pedidos</t>
   </si>
   <si>
-    <t xml:space="preserve">Todo pedido de entrega</t>
+    <t xml:space="preserve">Uma vez por noite: a maior espera, lida no fechamento</t>
   </si>
   <si>
     <t xml:space="preserve">Líder da expedição · Sistema de pedidos</t>
@@ -1035,7 +1035,7 @@
     <t xml:space="preserve">Termômetro de espeto, no centro da pizza</t>
   </si>
   <si>
-    <t xml:space="preserve">Três pedidos por hora</t>
+    <t xml:space="preserve">Uma pizza por noite, no pico</t>
   </si>
   <si>
     <t xml:space="preserve">Líder da expedição · Planilha da expedição</t>
@@ -1101,7 +1101,7 @@
     <t xml:space="preserve">Noite 12/03</t>
   </si>
   <si>
-    <t xml:space="preserve">Pedido conferido de novo antes de sair. Atendente do turno orientado.</t>
+    <t xml:space="preserve">Pedido sem rubrica segurado na saída e conferido com a etiqueta. Atendente do turno orientado.</t>
   </si>
   <si>
     <t xml:space="preserve">Saída priorizada. Nenhum pedido passou de 15 minutos.</t>
@@ -1227,6 +1227,9 @@
     <t xml:space="preserve">Bolsa nº 4 rasgada em 12/03. Plataforma avisada em 13/03; troca combinada.</t>
   </si>
   <si>
+    <t xml:space="preserve">Mudanças · registro lido em 31/03/2027</t>
+  </si>
+  <si>
     <t xml:space="preserve">Receita ajustada, com 2% a mais de água. Ficha da massa atualizada.</t>
   </si>
   <si>
@@ -1236,7 +1239,7 @@
     <t xml:space="preserve">Fila no forno na sexta à noite.</t>
   </si>
   <si>
-    <t xml:space="preserve">Dois entregadores extras nas sextas e nos sábados.</t>
+    <t xml:space="preserve">Mais dois entregadores extras nas sextas e nos sábados.</t>
   </si>
   <si>
     <t xml:space="preserve">Espera da pizza pronta acima de 10 minutos no pico.</t>
@@ -1557,7 +1560,7 @@
     <t xml:space="preserve">Segundo fornecedor homologado em 29/03.</t>
   </si>
   <si>
-    <t xml:space="preserve">Lote piloto de duas bobinas: espessura e solda ensaiadas.</t>
+    <t xml:space="preserve">Lote piloto 127, de 05/05/2027, com duas bobinas: espessura e solda ensaiadas.</t>
   </si>
   <si>
     <t xml:space="preserve">Gerente industrial</t>
@@ -2224,11 +2227,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="29397733"/>
-        <c:axId val="56989517"/>
+        <c:axId val="93060251"/>
+        <c:axId val="87982215"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="29397733"/>
+        <c:axId val="93060251"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2260,7 +2263,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56989517"/>
+        <c:crossAx val="87982215"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2268,7 +2271,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="56989517"/>
+        <c:axId val="87982215"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -2309,7 +2312,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29397733"/>
+        <c:crossAx val="93060251"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="0.25"/>
@@ -11987,7 +11990,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="10" t="s">
         <v>100</v>
       </c>
@@ -12020,7 +12023,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="10" t="s">
         <v>101</v>
       </c>
@@ -13584,7 +13587,7 @@
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
     </row>
-    <row r="70" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B70" s="38" t="n">
         <v>46458</v>
       </c>
@@ -14455,7 +14458,7 @@
     </row>
     <row r="103" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B103" s="40" t="s">
-        <v>48</v>
+        <v>354</v>
       </c>
       <c r="C103" s="40"/>
       <c r="D103" s="40"/>
@@ -14515,7 +14518,7 @@
         <v>188</v>
       </c>
       <c r="J105" s="7" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="13" t="str">
@@ -14528,10 +14531,10 @@
         <v>46458</v>
       </c>
       <c r="C106" s="32" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D106" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E106" s="7"/>
       <c r="F106" s="7"/>
@@ -14550,22 +14553,22 @@
         <v>46472</v>
       </c>
       <c r="C107" s="32" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D107" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F107" s="7"/>
       <c r="G107" s="7"/>
       <c r="H107" s="7"/>
       <c r="I107" s="7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="J107" s="7" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="13" t="str">
@@ -14608,7 +14611,7 @@
     </row>
     <row r="111" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B111" s="15" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C111" s="15"/>
       <c r="D111" s="15"/>
@@ -14662,7 +14665,7 @@
     </row>
     <row r="114" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B114" s="15" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C114" s="15"/>
       <c r="D114" s="15"/>
@@ -14953,7 +14956,7 @@
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="30" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E4" s="30"/>
       <c r="F4" s="30"/>
@@ -14970,7 +14973,7 @@
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="30" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E5" s="30"/>
       <c r="F5" s="30"/>
@@ -14987,7 +14990,7 @@
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="30" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E6" s="30"/>
       <c r="F6" s="30"/>
@@ -15004,7 +15007,7 @@
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="30" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E7" s="30"/>
       <c r="F7" s="30"/>
@@ -15021,7 +15024,7 @@
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="30" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E8" s="30"/>
       <c r="F8" s="30"/>
@@ -15038,7 +15041,7 @@
       </c>
       <c r="C9" s="4"/>
       <c r="D9" s="30" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E9" s="30"/>
       <c r="F9" s="30"/>
@@ -15104,10 +15107,10 @@
         <v>96</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D13" s="32" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E13" s="33" t="s">
         <v>255</v>
@@ -15119,19 +15122,19 @@
         <v>2.2</v>
       </c>
       <c r="H13" s="33" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15139,10 +15142,10 @@
         <v>97</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D14" s="32" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E14" s="33" t="s">
         <v>239</v>
@@ -15157,16 +15160,16 @@
         <v>248</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15174,10 +15177,10 @@
         <v>98</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E15" s="33" t="s">
         <v>255</v>
@@ -15189,19 +15192,19 @@
         <v>42</v>
       </c>
       <c r="H15" s="33" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15209,10 +15212,10 @@
         <v>99</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D16" s="32" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E16" s="33" t="s">
         <v>255</v>
@@ -15224,19 +15227,19 @@
         <v>602</v>
       </c>
       <c r="H16" s="33" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15244,10 +15247,10 @@
         <v>100</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E17" s="33" t="s">
         <v>255</v>
@@ -15258,16 +15261,16 @@
         <v>263</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15275,10 +15278,10 @@
         <v>101</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E18" s="33" t="s">
         <v>255</v>
@@ -15288,19 +15291,19 @@
       </c>
       <c r="G18" s="34"/>
       <c r="H18" s="33" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15308,10 +15311,10 @@
         <v>102</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D19" s="32" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E19" s="33" t="s">
         <v>255</v>
@@ -15322,16 +15325,16 @@
         <v>263</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15381,7 +15384,7 @@
         <v>96</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="28" t="n">
@@ -15413,7 +15416,7 @@
         <v>97</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D24" s="7"/>
       <c r="E24" s="28" t="n">
@@ -15445,7 +15448,7 @@
         <v>98</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="28" t="n">
@@ -15477,7 +15480,7 @@
         <v>99</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D26" s="7"/>
       <c r="E26" s="28" t="n">
@@ -15509,7 +15512,7 @@
         <v>100</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D27" s="7"/>
       <c r="E27" s="28" t="n">
@@ -15541,7 +15544,7 @@
         <v>101</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D28" s="7"/>
       <c r="E28" s="28" t="n">
@@ -15573,7 +15576,7 @@
         <v>102</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D29" s="7"/>
       <c r="E29" s="28" t="n">
@@ -15651,10 +15654,10 @@
         <v>46517</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D33" s="39" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E33" s="33" t="s">
         <v>96</v>
@@ -15683,10 +15686,10 @@
         <v>46517</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D34" s="39" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E34" s="33" t="s">
         <v>97</v>
@@ -15715,10 +15718,10 @@
         <v>46517</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="D35" s="39" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E35" s="33" t="s">
         <v>98</v>
@@ -15747,10 +15750,10 @@
         <v>46517</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D36" s="39" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E36" s="33" t="s">
         <v>98</v>
@@ -15779,10 +15782,10 @@
         <v>46517</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D37" s="39" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E37" s="33" t="s">
         <v>99</v>
@@ -15811,10 +15814,10 @@
         <v>46517</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D38" s="39" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E38" s="33" t="s">
         <v>100</v>
@@ -15843,10 +15846,10 @@
         <v>46517</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D39" s="39" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E39" s="33" t="s">
         <v>101</v>
@@ -15875,10 +15878,10 @@
         <v>46517</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D40" s="39" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E40" s="33" t="s">
         <v>102</v>
@@ -15907,10 +15910,10 @@
         <v>46518</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D41" s="39" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E41" s="33" t="s">
         <v>96</v>
@@ -15939,10 +15942,10 @@
         <v>46518</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D42" s="39" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E42" s="33" t="s">
         <v>97</v>
@@ -15971,10 +15974,10 @@
         <v>46518</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D43" s="39" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E43" s="33" t="s">
         <v>98</v>
@@ -16003,10 +16006,10 @@
         <v>46518</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D44" s="39" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E44" s="33" t="s">
         <v>98</v>
@@ -16035,10 +16038,10 @@
         <v>46518</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D45" s="39" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E45" s="33" t="s">
         <v>99</v>
@@ -16067,10 +16070,10 @@
         <v>46518</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D46" s="39" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E46" s="33" t="s">
         <v>100</v>
@@ -16084,14 +16087,14 @@
         <v/>
       </c>
       <c r="H46" s="34" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="I46" s="22" t="str">
         <f aca="false">IF(AND(F46="",G46=""),IF(H46="","Falta o resultado",IF(H46="Sim","Dentro","Fora")),IF(H46="","Falta o valor",IF(AND(OR(F46="",H46&gt;=F46),OR(G46="",H46&lt;=G46)),"Dentro","Fora")))</f>
         <v>Fora</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
@@ -16101,10 +16104,10 @@
         <v>46518</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D47" s="39" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E47" s="33" t="s">
         <v>101</v>
@@ -16133,10 +16136,10 @@
         <v>46518</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D48" s="39" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E48" s="33" t="s">
         <v>102</v>
@@ -16165,10 +16168,10 @@
         <v>46519</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D49" s="39" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E49" s="33" t="s">
         <v>96</v>
@@ -16197,10 +16200,10 @@
         <v>46519</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D50" s="39" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E50" s="33" t="s">
         <v>97</v>
@@ -16221,7 +16224,7 @@
         <v>Fora</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -16231,10 +16234,10 @@
         <v>46519</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D51" s="39" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E51" s="33" t="s">
         <v>98</v>
@@ -16255,7 +16258,7 @@
         <v>Fora</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
@@ -16265,10 +16268,10 @@
         <v>46519</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D52" s="39" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E52" s="33" t="s">
         <v>98</v>
@@ -16297,10 +16300,10 @@
         <v>46519</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D53" s="39" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E53" s="33" t="s">
         <v>99</v>
@@ -16329,10 +16332,10 @@
         <v>46519</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D54" s="39" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E54" s="33" t="s">
         <v>100</v>
@@ -16361,10 +16364,10 @@
         <v>46519</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D55" s="39" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E55" s="33" t="s">
         <v>101</v>
@@ -16393,10 +16396,10 @@
         <v>46519</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D56" s="39" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E56" s="33" t="s">
         <v>102</v>
@@ -16425,10 +16428,10 @@
         <v>46520</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D57" s="39" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E57" s="33" t="s">
         <v>96</v>
@@ -16457,10 +16460,10 @@
         <v>46520</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D58" s="39" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E58" s="33" t="s">
         <v>97</v>
@@ -16489,10 +16492,10 @@
         <v>46520</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D59" s="39" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E59" s="33" t="s">
         <v>98</v>
@@ -16521,10 +16524,10 @@
         <v>46520</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D60" s="39" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E60" s="33" t="s">
         <v>98</v>
@@ -16553,10 +16556,10 @@
         <v>46520</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D61" s="39" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E61" s="33" t="s">
         <v>99</v>
@@ -16585,10 +16588,10 @@
         <v>46520</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D62" s="39" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E62" s="33" t="s">
         <v>100</v>
@@ -16617,10 +16620,10 @@
         <v>46520</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D63" s="39" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E63" s="33" t="s">
         <v>101</v>
@@ -16649,10 +16652,10 @@
         <v>46520</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D64" s="39" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E64" s="33" t="s">
         <v>102</v>
@@ -16666,7 +16669,7 @@
         <v/>
       </c>
       <c r="H64" s="34" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="I64" s="22" t="str">
         <f aca="false">IF(AND(F64="",G64=""),IF(H64="","Falta o resultado",IF(H64="Sim","Dentro","Fora")),IF(H64="","Falta o valor",IF(AND(OR(F64="",H64&gt;=F64),OR(G64="",H64&lt;=G64)),"Dentro","Fora")))</f>
@@ -16681,10 +16684,10 @@
         <v>46521</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D65" s="39" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E65" s="33" t="s">
         <v>96</v>
@@ -16713,10 +16716,10 @@
         <v>46521</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D66" s="39" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E66" s="33" t="s">
         <v>97</v>
@@ -16745,10 +16748,10 @@
         <v>46521</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D67" s="39" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E67" s="33" t="s">
         <v>98</v>
@@ -16769,7 +16772,7 @@
         <v>Fora</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -16779,10 +16782,10 @@
         <v>46521</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D68" s="39" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E68" s="33" t="s">
         <v>98</v>
@@ -16811,10 +16814,10 @@
         <v>46521</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D69" s="39" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E69" s="33" t="s">
         <v>99</v>
@@ -16843,10 +16846,10 @@
         <v>46521</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D70" s="39" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E70" s="33" t="s">
         <v>100</v>
@@ -16875,10 +16878,10 @@
         <v>46521</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D71" s="39" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E71" s="33" t="s">
         <v>101</v>
@@ -16907,10 +16910,10 @@
         <v>46521</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="D72" s="39" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E72" s="33" t="s">
         <v>102</v>
@@ -16979,23 +16982,23 @@
         <v>1</v>
       </c>
       <c r="C76" s="32" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F76" s="7"/>
       <c r="G76" s="7"/>
       <c r="H76" s="7"/>
       <c r="I76" s="7" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="J76" s="7"/>
       <c r="K76" s="7" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L76" s="7"/>
     </row>
@@ -17004,23 +17007,23 @@
         <v>2</v>
       </c>
       <c r="C77" s="32" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F77" s="7"/>
       <c r="G77" s="7"/>
       <c r="H77" s="7"/>
       <c r="I77" s="7" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J77" s="7"/>
       <c r="K77" s="7" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L77" s="7"/>
     </row>
@@ -17029,23 +17032,23 @@
         <v>3</v>
       </c>
       <c r="C78" s="32" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F78" s="7"/>
       <c r="G78" s="7"/>
       <c r="H78" s="7"/>
       <c r="I78" s="7" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="J78" s="7"/>
       <c r="K78" s="7" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L78" s="7"/>
     </row>
@@ -17054,23 +17057,23 @@
         <v>4</v>
       </c>
       <c r="C79" s="32" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F79" s="7"/>
       <c r="G79" s="7"/>
       <c r="H79" s="7"/>
       <c r="I79" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="J79" s="7"/>
       <c r="K79" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="L79" s="7"/>
     </row>
@@ -17079,23 +17082,23 @@
         <v>5</v>
       </c>
       <c r="C80" s="32" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F80" s="7"/>
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
       <c r="I80" s="7" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="J80" s="7"/>
       <c r="K80" s="7" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L80" s="7"/>
     </row>
@@ -17144,22 +17147,22 @@
         <v>1</v>
       </c>
       <c r="C84" s="32" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E84" s="33" t="s">
         <v>347</v>
       </c>
       <c r="F84" s="33"/>
       <c r="G84" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H84" s="7"/>
       <c r="I84" s="7"/>
       <c r="J84" s="7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -17169,17 +17172,17 @@
         <v>2</v>
       </c>
       <c r="C85" s="32" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E85" s="33" t="s">
         <v>347</v>
       </c>
       <c r="F85" s="33"/>
       <c r="G85" s="7" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H85" s="7"/>
       <c r="I85" s="7"/>
@@ -17192,17 +17195,17 @@
         <v>3</v>
       </c>
       <c r="C86" s="32" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E86" s="33" t="s">
         <v>351</v>
       </c>
       <c r="F86" s="33"/>
       <c r="G86" s="7" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H86" s="7"/>
       <c r="I86" s="7"/>
@@ -17257,17 +17260,17 @@
         <v>46510</v>
       </c>
       <c r="C90" s="32" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E90" s="7"/>
       <c r="F90" s="7"/>
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
       <c r="I90" s="7" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="J90" s="7"/>
       <c r="K90" s="7"/>
@@ -17281,22 +17284,22 @@
         <v>46521</v>
       </c>
       <c r="C91" s="32" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F91" s="7"/>
       <c r="G91" s="7"/>
       <c r="H91" s="7"/>
       <c r="I91" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="13" t="str">
@@ -17339,7 +17342,7 @@
     </row>
     <row r="95" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B95" s="15" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C95" s="15"/>
       <c r="D95" s="15"/>
@@ -17393,7 +17396,7 @@
     </row>
     <row r="98" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B98" s="15" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C98" s="15"/>
       <c r="D98" s="15"/>

--- a/Producao/Producao-modelo.xlsx
+++ b/Producao/Producao-modelo.xlsx
@@ -163,7 +163,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="471">
   <si>
     <t xml:space="preserve">Controle de produção e de serviço — Como usar esta planilha</t>
   </si>
@@ -972,13 +972,13 @@
     <t xml:space="preserve">Assar</t>
   </si>
   <si>
-    <t xml:space="preserve">Temperatura do forno</t>
+    <t xml:space="preserve">Temperatura do forno no pico: a pior leitura da noite</t>
   </si>
   <si>
     <t xml:space="preserve">Termômetro do forno, no pico do turno</t>
   </si>
   <si>
-    <t xml:space="preserve">Uma vez por noite, no pico</t>
+    <t xml:space="preserve">A cada hora do pico; registra-se a leitura fora da faixa ou, com todas dentro, a mais afastada de 300 °C</t>
   </si>
   <si>
     <t xml:space="preserve">Pizzaiolo do turno · Registro de regulagem do forno</t>
@@ -999,7 +999,7 @@
     <t xml:space="preserve">Conferência da pizza com a etiqueta, na saída, antes de o pedido sair</t>
   </si>
   <si>
-    <t xml:space="preserve">Uma amostra de 20 pedidos por noite, somada no fechamento</t>
+    <t xml:space="preserve">20 pedidos por noite, conferidos na saída durante o pico; o fechamento registra quantos tinham a rubrica</t>
   </si>
   <si>
     <t xml:space="preserve">Quem embala · Etiqueta rubricada</t>
@@ -1020,7 +1020,7 @@
     <t xml:space="preserve">Horários de pronto e de saída, no sistema de pedidos</t>
   </si>
   <si>
-    <t xml:space="preserve">Uma vez por noite: a maior espera, lida no fechamento</t>
+    <t xml:space="preserve">Acompanhada no sistema durante a noite; a maior espera é registrada no fechamento</t>
   </si>
   <si>
     <t xml:space="preserve">Líder da expedição · Sistema de pedidos</t>
@@ -1029,13 +1029,13 @@
     <t xml:space="preserve">Priorizar a saída. Acima de 15 minutos, refazer a pizza.</t>
   </si>
   <si>
-    <t xml:space="preserve">Temperatura da pizza na saída</t>
+    <t xml:space="preserve">Menor temperatura da pizza na saída, na noite</t>
   </si>
   <si>
     <t xml:space="preserve">Termômetro de espeto, no centro da pizza</t>
   </si>
   <si>
-    <t xml:space="preserve">Uma pizza por noite, no pico</t>
+    <t xml:space="preserve">Três pizzas por hora no pico; registra-se a menor temperatura da noite</t>
   </si>
   <si>
     <t xml:space="preserve">Líder da expedição · Planilha da expedição</t>
@@ -1308,7 +1308,7 @@
     <t xml:space="preserve">Leitura no painel da extrusora</t>
   </si>
   <si>
-    <t xml:space="preserve">A cada duas horas</t>
+    <t xml:space="preserve">A cada duas horas; a folha registra, por lote, a leitura mais afastada de 190 °C</t>
   </si>
   <si>
     <t xml:space="preserve">Operador · Folha de processo</t>
@@ -1341,6 +1341,9 @@
     <t xml:space="preserve">Trena calibrada TR-03</t>
   </si>
   <si>
+    <t xml:space="preserve">Cada bobina; a folha registra, por lote, a largura mais afastada de 600 mm</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ajustar as guias e segregar a bobina.</t>
   </si>
   <si>
@@ -1353,6 +1356,9 @@
     <t xml:space="preserve">Exame visual, com o padrão de defeitos do posto</t>
   </si>
   <si>
+    <t xml:space="preserve">Cada bobina; a folha registra, por lote, se todas as bobinas estão conformes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Segregar a bobina e procurar a origem: filtro, matriz ou resina.</t>
   </si>
   <si>
@@ -1384,6 +1390,9 @@
   </si>
   <si>
     <t xml:space="preserve">Conferência da etiqueta com a folha de processo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cada bobina; o romaneio registra, por lote, se todas as etiquetas conferem</t>
   </si>
   <si>
     <t xml:space="preserve">Expedição · Romaneio</t>
@@ -2227,11 +2236,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="93060251"/>
-        <c:axId val="87982215"/>
+        <c:axId val="27791634"/>
+        <c:axId val="83319045"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="93060251"/>
+        <c:axId val="27791634"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2263,7 +2272,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="87982215"/>
+        <c:crossAx val="83319045"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2271,7 +2280,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="87982215"/>
+        <c:axId val="83319045"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -2312,7 +2321,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="93060251"/>
+        <c:crossAx val="27791634"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="0.25"/>
@@ -11955,7 +11964,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="10" t="s">
         <v>99</v>
       </c>
@@ -11990,7 +11999,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="10" t="s">
         <v>100</v>
       </c>
@@ -12023,7 +12032,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="10" t="s">
         <v>101</v>
       </c>
@@ -12056,7 +12065,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="10" t="s">
         <v>102</v>
       </c>
@@ -15137,7 +15146,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="10" t="s">
         <v>97</v>
       </c>
@@ -15207,7 +15216,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="10" t="s">
         <v>99</v>
       </c>
@@ -15233,24 +15242,24 @@
         <v>391</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="K16" s="7" t="s">
         <v>382</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="10" t="s">
         <v>100</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E17" s="33" t="s">
         <v>255</v>
@@ -15261,16 +15270,16 @@
         <v>263</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="K17" s="7" t="s">
         <v>382</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15278,10 +15287,10 @@
         <v>101</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E18" s="33" t="s">
         <v>255</v>
@@ -15291,30 +15300,30 @@
       </c>
       <c r="G18" s="34"/>
       <c r="H18" s="33" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="10" t="s">
         <v>102</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D19" s="32" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E19" s="33" t="s">
         <v>255</v>
@@ -15325,16 +15334,16 @@
         <v>263</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>387</v>
+        <v>409</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15512,7 +15521,7 @@
         <v>100</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D27" s="7"/>
       <c r="E27" s="28" t="n">
@@ -15544,7 +15553,7 @@
         <v>101</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D28" s="7"/>
       <c r="E28" s="28" t="n">
@@ -15576,7 +15585,7 @@
         <v>102</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D29" s="7"/>
       <c r="E29" s="28" t="n">
@@ -15654,7 +15663,7 @@
         <v>46517</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D33" s="39" t="s">
         <v>372</v>
@@ -15686,7 +15695,7 @@
         <v>46517</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D34" s="39" t="s">
         <v>379</v>
@@ -15718,7 +15727,7 @@
         <v>46517</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="D35" s="39" t="s">
         <v>384</v>
@@ -15750,7 +15759,7 @@
         <v>46517</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="D36" s="39" t="s">
         <v>384</v>
@@ -15782,7 +15791,7 @@
         <v>46517</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D37" s="39" t="s">
         <v>389</v>
@@ -15814,10 +15823,10 @@
         <v>46517</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D38" s="39" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E38" s="33" t="s">
         <v>100</v>
@@ -15846,10 +15855,10 @@
         <v>46517</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D39" s="39" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E39" s="33" t="s">
         <v>101</v>
@@ -15878,10 +15887,10 @@
         <v>46517</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="D40" s="39" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E40" s="33" t="s">
         <v>102</v>
@@ -15910,7 +15919,7 @@
         <v>46518</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D41" s="39" t="s">
         <v>372</v>
@@ -15942,7 +15951,7 @@
         <v>46518</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D42" s="39" t="s">
         <v>379</v>
@@ -15974,7 +15983,7 @@
         <v>46518</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="D43" s="39" t="s">
         <v>384</v>
@@ -16006,7 +16015,7 @@
         <v>46518</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="D44" s="39" t="s">
         <v>384</v>
@@ -16038,7 +16047,7 @@
         <v>46518</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D45" s="39" t="s">
         <v>389</v>
@@ -16070,10 +16079,10 @@
         <v>46518</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D46" s="39" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E46" s="33" t="s">
         <v>100</v>
@@ -16087,14 +16096,14 @@
         <v/>
       </c>
       <c r="H46" s="34" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="I46" s="22" t="str">
         <f aca="false">IF(AND(F46="",G46=""),IF(H46="","Falta o resultado",IF(H46="Sim","Dentro","Fora")),IF(H46="","Falta o valor",IF(AND(OR(F46="",H46&gt;=F46),OR(G46="",H46&lt;=G46)),"Dentro","Fora")))</f>
         <v>Fora</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
@@ -16104,10 +16113,10 @@
         <v>46518</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D47" s="39" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E47" s="33" t="s">
         <v>101</v>
@@ -16136,10 +16145,10 @@
         <v>46518</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="D48" s="39" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E48" s="33" t="s">
         <v>102</v>
@@ -16168,7 +16177,7 @@
         <v>46519</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D49" s="39" t="s">
         <v>372</v>
@@ -16200,7 +16209,7 @@
         <v>46519</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D50" s="39" t="s">
         <v>379</v>
@@ -16224,7 +16233,7 @@
         <v>Fora</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -16234,7 +16243,7 @@
         <v>46519</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="D51" s="39" t="s">
         <v>384</v>
@@ -16258,7 +16267,7 @@
         <v>Fora</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
@@ -16268,7 +16277,7 @@
         <v>46519</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="D52" s="39" t="s">
         <v>384</v>
@@ -16300,7 +16309,7 @@
         <v>46519</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D53" s="39" t="s">
         <v>389</v>
@@ -16332,10 +16341,10 @@
         <v>46519</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D54" s="39" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E54" s="33" t="s">
         <v>100</v>
@@ -16364,10 +16373,10 @@
         <v>46519</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D55" s="39" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E55" s="33" t="s">
         <v>101</v>
@@ -16396,10 +16405,10 @@
         <v>46519</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D56" s="39" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E56" s="33" t="s">
         <v>102</v>
@@ -16428,7 +16437,7 @@
         <v>46520</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D57" s="39" t="s">
         <v>372</v>
@@ -16460,7 +16469,7 @@
         <v>46520</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D58" s="39" t="s">
         <v>379</v>
@@ -16492,7 +16501,7 @@
         <v>46520</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="D59" s="39" t="s">
         <v>384</v>
@@ -16524,7 +16533,7 @@
         <v>46520</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D60" s="39" t="s">
         <v>384</v>
@@ -16556,7 +16565,7 @@
         <v>46520</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D61" s="39" t="s">
         <v>389</v>
@@ -16588,10 +16597,10 @@
         <v>46520</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D62" s="39" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E62" s="33" t="s">
         <v>100</v>
@@ -16620,10 +16629,10 @@
         <v>46520</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D63" s="39" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E63" s="33" t="s">
         <v>101</v>
@@ -16652,10 +16661,10 @@
         <v>46520</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="D64" s="39" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E64" s="33" t="s">
         <v>102</v>
@@ -16669,7 +16678,7 @@
         <v/>
       </c>
       <c r="H64" s="34" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="I64" s="22" t="str">
         <f aca="false">IF(AND(F64="",G64=""),IF(H64="","Falta o resultado",IF(H64="Sim","Dentro","Fora")),IF(H64="","Falta o valor",IF(AND(OR(F64="",H64&gt;=F64),OR(G64="",H64&lt;=G64)),"Dentro","Fora")))</f>
@@ -16684,7 +16693,7 @@
         <v>46521</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D65" s="39" t="s">
         <v>372</v>
@@ -16716,7 +16725,7 @@
         <v>46521</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D66" s="39" t="s">
         <v>379</v>
@@ -16748,7 +16757,7 @@
         <v>46521</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="D67" s="39" t="s">
         <v>384</v>
@@ -16772,7 +16781,7 @@
         <v>Fora</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -16782,7 +16791,7 @@
         <v>46521</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="D68" s="39" t="s">
         <v>384</v>
@@ -16814,7 +16823,7 @@
         <v>46521</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D69" s="39" t="s">
         <v>389</v>
@@ -16846,10 +16855,10 @@
         <v>46521</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D70" s="39" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E70" s="33" t="s">
         <v>100</v>
@@ -16878,10 +16887,10 @@
         <v>46521</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D71" s="39" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E71" s="33" t="s">
         <v>101</v>
@@ -16910,10 +16919,10 @@
         <v>46521</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D72" s="39" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E72" s="33" t="s">
         <v>102</v>
@@ -16985,20 +16994,20 @@
         <v>371</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="F76" s="7"/>
       <c r="G76" s="7"/>
       <c r="H76" s="7"/>
       <c r="I76" s="7" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="J76" s="7"/>
       <c r="K76" s="7" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="L76" s="7"/>
     </row>
@@ -17010,20 +17019,20 @@
         <v>378</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F77" s="7"/>
       <c r="G77" s="7"/>
       <c r="H77" s="7"/>
       <c r="I77" s="7" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="J77" s="7"/>
       <c r="K77" s="7" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="L77" s="7"/>
     </row>
@@ -17032,23 +17041,23 @@
         <v>3</v>
       </c>
       <c r="C78" s="32" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="F78" s="7"/>
       <c r="G78" s="7"/>
       <c r="H78" s="7"/>
       <c r="I78" s="7" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="J78" s="7"/>
       <c r="K78" s="7" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="L78" s="7"/>
     </row>
@@ -17057,23 +17066,23 @@
         <v>4</v>
       </c>
       <c r="C79" s="32" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="F79" s="7"/>
       <c r="G79" s="7"/>
       <c r="H79" s="7"/>
       <c r="I79" s="7" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="J79" s="7"/>
       <c r="K79" s="7" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="L79" s="7"/>
     </row>
@@ -17082,23 +17091,23 @@
         <v>5</v>
       </c>
       <c r="C80" s="32" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D80" s="7" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="F80" s="7"/>
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
       <c r="I80" s="7" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="J80" s="7"/>
       <c r="K80" s="7" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="L80" s="7"/>
     </row>
@@ -17147,22 +17156,22 @@
         <v>1</v>
       </c>
       <c r="C84" s="32" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="E84" s="33" t="s">
         <v>347</v>
       </c>
       <c r="F84" s="33"/>
       <c r="G84" s="7" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="H84" s="7"/>
       <c r="I84" s="7"/>
       <c r="J84" s="7" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -17172,17 +17181,17 @@
         <v>2</v>
       </c>
       <c r="C85" s="32" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="D85" s="7" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="E85" s="33" t="s">
         <v>347</v>
       </c>
       <c r="F85" s="33"/>
       <c r="G85" s="7" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="H85" s="7"/>
       <c r="I85" s="7"/>
@@ -17195,17 +17204,17 @@
         <v>3</v>
       </c>
       <c r="C86" s="32" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="D86" s="7" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="E86" s="33" t="s">
         <v>351</v>
       </c>
       <c r="F86" s="33"/>
       <c r="G86" s="7" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="H86" s="7"/>
       <c r="I86" s="7"/>
@@ -17260,17 +17269,17 @@
         <v>46510</v>
       </c>
       <c r="C90" s="32" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="E90" s="7"/>
       <c r="F90" s="7"/>
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
       <c r="I90" s="7" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="J90" s="7"/>
       <c r="K90" s="7"/>
@@ -17284,22 +17293,22 @@
         <v>46521</v>
       </c>
       <c r="C91" s="32" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="D91" s="7" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="F91" s="7"/>
       <c r="G91" s="7"/>
       <c r="H91" s="7"/>
       <c r="I91" s="7" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="13" t="str">

--- a/Producao/Producao-modelo.xlsx
+++ b/Producao/Producao-modelo.xlsx
@@ -915,7 +915,7 @@
     <t xml:space="preserve">Termômetro da câmara, leitura no visor</t>
   </si>
   <si>
-    <t xml:space="preserve">Duas leituras por noite</t>
+    <t xml:space="preserve">Duas leituras por dia, uma em cada turno</t>
   </si>
   <si>
     <t xml:space="preserve">Pizzaiolo do turno · Planilha de temperatura (FR-02)</t>
@@ -2236,11 +2236,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="27791634"/>
-        <c:axId val="83319045"/>
+        <c:axId val="51759097"/>
+        <c:axId val="61958395"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="27791634"/>
+        <c:axId val="51759097"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2272,7 +2272,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83319045"/>
+        <c:crossAx val="61958395"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2280,7 +2280,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="83319045"/>
+        <c:axId val="61958395"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -2321,7 +2321,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27791634"/>
+        <c:crossAx val="51759097"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="0.25"/>
